--- a/939/月供計劃-939建銀.xlsx
+++ b/939/月供計劃-939建銀.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\桌面\939 Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\桌面\Python\939\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886D4575-87D6-41C6-AA42-57E19174A600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4663C024-A2C4-4261-A46C-4323277E0457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>日期</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -586,20 +586,44 @@
     <xf numFmtId="178" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="178" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="178" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -630,30 +654,6 @@
     </xf>
     <xf numFmtId="177" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1035,19 +1035,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
       <c r="L1" s="29" t="s">
         <v>22</v>
       </c>
@@ -1056,22 +1056,22 @@
       <c r="A2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="48">
         <f>(I5/15000)*100%</f>
-        <v>1.3780000000000001E-2</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43" t="str">
+        <v>2.0126666666666668E-2</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="51" t="str">
         <f>IF(B2&gt;=1, "達成財務自由！", "加油！仲有 " &amp; TEXT(1-B2, "0%") &amp; " 就供完喇")</f>
-        <v>加油！仲有 99% 就供完喇</v>
-      </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
+        <v>加油！仲有 98% 就供完喇</v>
+      </c>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
       <c r="L2" s="28" t="s">
         <v>20</v>
       </c>
@@ -1084,16 +1084,16 @@
       <c r="A3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="53">
         <f>LOOKUP(9.99999999999999E+307,I:I )</f>
-        <v>6201</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47"/>
+        <v>9057</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -1109,24 +1109,24 @@
       <c r="A4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="38">
         <f>SUM(G10:G1004)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="33" t="s">
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="34"/>
-      <c r="I4" s="35">
+      <c r="H4" s="42"/>
+      <c r="I4" s="38">
         <f>LOOKUP(9.99999999999999E+307,I:I )*K7</f>
-        <v>2480.4</v>
-      </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+        <v>3622.8</v>
+      </c>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
       <c r="L4" s="28" t="s">
         <v>30</v>
       </c>
@@ -1144,24 +1144,24 @@
       <c r="A5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="38">
         <f>LOOKUP(9.99999999999999E+307,K:K )</f>
-        <v>46337.899999999994</v>
-      </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="33" t="s">
+        <v>66229.899999999994</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35">
+      <c r="H5" s="42"/>
+      <c r="I5" s="38">
         <f>I4/12</f>
-        <v>206.70000000000002</v>
-      </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="37"/>
+        <v>301.90000000000003</v>
+      </c>
+      <c r="J5" s="39"/>
+      <c r="K5" s="40"/>
       <c r="L5" s="28" t="s">
         <v>21</v>
       </c>
@@ -1179,21 +1179,21 @@
       <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="43">
         <f>B4/B5</f>
         <v>0</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="33" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="42"/>
       <c r="I6" s="13">
         <f>LOOKUP(MAX(J:J)+1,J:J)</f>
-        <v>7.4726495726495719</v>
+        <v>7.3125648669537364</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>27</v>
@@ -1218,18 +1218,18 @@
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="38">
         <f>(LOOKUP(9.99999999999999E+307,I:I )*I7)+B4-B5</f>
-        <v>6370.6000000000058</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="33" t="s">
+        <v>10754.600000000006</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="55"/>
+      <c r="H7" s="45"/>
       <c r="I7" s="13">
         <v>8.5</v>
       </c>
@@ -1253,24 +1253,24 @@
       <c r="R7"/>
     </row>
     <row r="8" spans="1:18" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="52"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="37"/>
     </row>
     <row r="9" spans="1:18" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="9" t="s">
         <v>2</v>
       </c>
@@ -1415,15 +1415,15 @@
         <v>50</v>
       </c>
       <c r="I12" s="22">
-        <f t="shared" ref="I12:I13" si="1">I11+E12+C12</f>
+        <f t="shared" ref="I12:I15" si="1">I11+E12+C12</f>
         <v>4773</v>
       </c>
       <c r="J12" s="23">
-        <f t="shared" ref="J12:J13" si="2">(K11+(E12*F12+C12*D12-H12))/I12</f>
+        <f t="shared" ref="J12:J15" si="2">(K11+(E12*F12+C12*D12-H12))/I12</f>
         <v>7.6245338361617421</v>
       </c>
       <c r="K12" s="23">
-        <f t="shared" ref="K12:K13" si="3">J12*I12</f>
+        <f t="shared" ref="K12:K15" si="3">J12*I12</f>
         <v>36391.899999999994</v>
       </c>
       <c r="L12" s="24" t="s">
@@ -1476,32 +1476,84 @@
       <c r="A14" s="19">
         <v>46517</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
+      <c r="B14" s="30">
+        <v>16500</v>
+      </c>
+      <c r="C14" s="21">
+        <v>0</v>
+      </c>
+      <c r="D14" s="20">
+        <v>0</v>
+      </c>
+      <c r="E14" s="25">
+        <v>1428</v>
+      </c>
+      <c r="F14" s="20">
+        <v>7</v>
+      </c>
+      <c r="G14" s="20">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
+        <v>50</v>
+      </c>
+      <c r="I14" s="22">
+        <f t="shared" si="1"/>
+        <v>7629</v>
+      </c>
+      <c r="J14" s="23">
+        <f t="shared" si="2"/>
+        <v>7.3776248525363739</v>
+      </c>
+      <c r="K14" s="23">
+        <f t="shared" si="3"/>
+        <v>56283.899999999994</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>9</v>
+      </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
         <v>46548</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
+      <c r="B15" s="30">
+        <v>16500</v>
+      </c>
+      <c r="C15" s="21">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20">
+        <v>0</v>
+      </c>
+      <c r="E15" s="25">
+        <v>1428</v>
+      </c>
+      <c r="F15" s="20">
+        <v>7</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
+        <v>50</v>
+      </c>
+      <c r="I15" s="22">
+        <f t="shared" si="1"/>
+        <v>9057</v>
+      </c>
+      <c r="J15" s="23">
+        <f t="shared" si="2"/>
+        <v>7.3125648669537364</v>
+      </c>
+      <c r="K15" s="23">
+        <f t="shared" si="3"/>
+        <v>66229.899999999994</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>9</v>
+      </c>
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:18" thickBot="1" x14ac:dyDescent="0.3">
@@ -2399,6 +2451,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:K8"/>
     <mergeCell ref="B5:F5"/>
@@ -2408,13 +2467,6 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="B3:H3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B6:F6">
